--- a/data/trans_orig/cron_mort_index-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/cron_mort_index-Estudios-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Índice de cronicidad física en base a la mortalidad</t>
+          <t>Índice de cronicidad física en base a la mortalidad (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,7 +731,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,45; 0,57</t>
+          <t>0,45; 0,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -741,17 +741,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,23</t>
+          <t>0,19; 0,24</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,2; 0,26</t>
+          <t>0,2; 0,25</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,46; 0,53</t>
+          <t>0,45; 0,53</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,46; 0,53</t>
+          <t>0,47; 0,53</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,07</t>
+          <t>0,04; 0,07</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,03; 0,07</t>
+          <t>0,03; 0,08</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,08</t>
+          <t>0,04; 0,09</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,25</t>
+          <t>0,18; 0,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,27</t>
+          <t>0,19; 0,26</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,2; 0,25</t>
+          <t>0,19; 0,25</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/cron_mort_index-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/cron_mort_index-Estudios-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,5</t>
+          <t>0,48</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,5</t>
+          <t>0,49</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,45; 0,56</t>
+          <t>0,43; 0,53</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,2; 0,25</t>
+          <t>0,2; 0,26</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,47; 0,53</t>
+          <t>0,45; 0,52</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,17</t>
+          <t>0,19</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,16</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,12; 0,2</t>
+          <t>0,17; 0,21</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -886,12 +886,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,07</t>
+          <t>0,05; 0,07</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,12; 0,25</t>
+          <t>0,13; 0,16</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,06</t>
+          <t>0,04; 0,05</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,14; 0,21</t>
+          <t>0,16; 0,18</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,19</t>
+          <t>0,2</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,11</t>
+          <t>0,12</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,16</t>
         </is>
       </c>
     </row>
@@ -1006,12 +1006,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,03; 0,08</t>
+          <t>0,03; 0,07</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,22</t>
+          <t>0,17; 0,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,09</t>
+          <t>0,04; 0,08</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,14</t>
+          <t>0,1; 0,14</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,13; 0,17</t>
+          <t>0,14; 0,18</t>
         </is>
       </c>
     </row>
@@ -1083,47 +1083,47 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
+          <t>0,24</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,07</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,11</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0,1</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>0,22</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,07</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,11</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0,06</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0,1</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0,22</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>0,06</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>0,1</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>0,1</t>
-        </is>
-      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,22</t>
+          <t>0,23</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,25</t>
+          <t>0,22; 0,26</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,26</t>
+          <t>0,2; 0,23</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,25</t>
+          <t>0,22; 0,24</t>
         </is>
       </c>
     </row>
